--- a/devnet-stress-vectors/devnet_plots.xlsx
+++ b/devnet-stress-vectors/devnet_plots.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zeronode-my.sharepoint.com/personal/ashok_zeronode_ca/Documents/Ashok/SFU- SustainableEnergyEngineering/Sustainable Energy &amp; Datacenter Models Tools/EnergySystemAnalysis- PyPSA/pypsa-zn/denvnet-stress-vectors/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zeronode-my.sharepoint.com/personal/ashok_zeronode_ca/Documents/Ashok/SFU- SustainableEnergyEngineering/Sustainable Energy &amp; Datacenter Models Tools/EnergySystemAnalysis- PyPSA/pypsa-zn/devnet-stress-vectors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="284" documentId="8_{1DE9AB68-969B-4576-8842-DCCCDAC6DEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86AAF940-6173-4F6D-AD88-3C873BD4FC2B}"/>
+  <xr:revisionPtr revIDLastSave="303" documentId="8_{1DE9AB68-969B-4576-8842-DCCCDAC6DEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71AF6F6C-4B56-4562-9884-0DC3BCC9B072}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12165" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{7340CB05-3689-448E-B208-BC226AF7FE68}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7340CB05-3689-448E-B208-BC226AF7FE68}"/>
   </bookViews>
   <sheets>
     <sheet name="DevNetGen_mc&lt;&gt;LMP" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="86">
   <si>
     <t>case</t>
   </si>
@@ -294,6 +294,36 @@
   <si>
     <t>Each line effective
 (MW)</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>c3</t>
+  </si>
+  <si>
+    <t>c4</t>
+  </si>
+  <si>
+    <t>c5</t>
+  </si>
+  <si>
+    <t>c6</t>
+  </si>
+  <si>
+    <t>c7</t>
+  </si>
+  <si>
+    <t>c8</t>
+  </si>
+  <si>
+    <t>c9</t>
+  </si>
+  <si>
+    <t>c10</t>
   </si>
 </sst>
 </file>
@@ -508,7 +538,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'DevNetGen_mc&lt;&gt;LMP'!$K$5</c:f>
+              <c:f>'DevNetGen_mc&lt;&gt;LMP'!$L$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -571,7 +601,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DevNetGen_mc&lt;&gt;LMP'!$K$6:$K$15</c:f>
+              <c:f>'DevNetGen_mc&lt;&gt;LMP'!$L$6:$L$15</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="10"/>
@@ -597,13 +627,13 @@
                   <c:v>2050000</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>1753000</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>1790000</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>1910000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1753000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -841,7 +871,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'DevNetGen_mc&lt;&gt;LMP'!$K$5</c:f>
+              <c:f>'DevNetGen_mc&lt;&gt;LMP'!$L$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -865,7 +895,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'DevNetGen_mc&lt;&gt;LMP'!$L$6:$L$15</c:f>
+              <c:f>'DevNetGen_mc&lt;&gt;LMP'!$M$6:$M$15</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="10"/>
@@ -894,17 +924,17 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>20</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DevNetGen_mc&lt;&gt;LMP'!$K$6:$K$15</c:f>
+              <c:f>'DevNetGen_mc&lt;&gt;LMP'!$L$6:$L$15</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="10"/>
@@ -930,13 +960,13 @@
                   <c:v>2050000</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>1753000</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>1790000</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>1910000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1753000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3211,15 +3241,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>462676</xdr:colOff>
+      <xdr:colOff>1295638</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>59293</xdr:rowOff>
+      <xdr:rowOff>55483</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>17859</xdr:colOff>
+      <xdr:colOff>1194196</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>131206</xdr:rowOff>
+      <xdr:rowOff>135016</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3246,16 +3276,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>976312</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>361473</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>55722</xdr:rowOff>
+      <xdr:rowOff>59532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>914876</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>303847</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3647,31 +3677,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FD17620-D246-448C-BD50-9E2A876F1E1F}">
-  <dimension ref="B2:T15"/>
+  <dimension ref="B2:U15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="8" width="10.77734375" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="8.77734375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="20.77734375" style="1" customWidth="1"/>
-    <col min="12" max="14" width="15.77734375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="25.77734375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20.77734375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="25.77734375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="20.77734375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="25.77734375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="20.77734375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="1.77734375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.88671875" style="1"/>
+    <col min="11" max="11" width="8.77734375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="20.77734375" style="1" customWidth="1"/>
+    <col min="13" max="15" width="15.77734375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="25.77734375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="25.77734375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="20.77734375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="25.77734375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="20.77734375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="1.77734375" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>56</v>
       </c>
@@ -3679,7 +3709,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -3691,13 +3721,13 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="2:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>0</v>
       </c>
@@ -3721,40 +3751,43 @@
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="O5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="Q5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="R5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="S5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="T5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T5" s="5" t="s">
+      <c r="U5" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B6" s="8">
         <v>1</v>
       </c>
@@ -3776,41 +3809,44 @@
       <c r="H6" s="7">
         <v>50</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="8">
+      <c r="L6" s="8">
         <v>2210000</v>
       </c>
-      <c r="L6" s="8">
+      <c r="M6" s="8">
         <v>0</v>
       </c>
-      <c r="M6" s="7">
+      <c r="N6" s="7">
         <v>1</v>
       </c>
-      <c r="N6" s="8">
+      <c r="O6" s="8">
         <v>1</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="P6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="P6" s="12" t="s">
+      <c r="Q6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="R6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="R6" s="12" t="s">
+      <c r="S6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="11" t="s">
+      <c r="T6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="T6" s="12" t="s">
+      <c r="U6" s="12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="8">
         <v>2</v>
       </c>
@@ -3832,41 +3868,44 @@
       <c r="H7" s="7">
         <v>70</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="8">
+      <c r="L7" s="8">
         <v>2210000</v>
       </c>
-      <c r="L7" s="8">
+      <c r="M7" s="8">
         <v>0</v>
       </c>
-      <c r="M7" s="7">
+      <c r="N7" s="7">
         <v>1</v>
       </c>
-      <c r="N7" s="8">
+      <c r="O7" s="8">
         <v>1</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="P7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="P7" s="12" t="s">
+      <c r="Q7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="R7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="R7" s="12" t="s">
+      <c r="S7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="S7" s="11" t="s">
+      <c r="T7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="T7" s="12" t="s">
+      <c r="U7" s="12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B8" s="8">
         <v>3</v>
       </c>
@@ -3888,41 +3927,44 @@
       <c r="H8" s="7">
         <v>70</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K8" s="8">
+      <c r="L8" s="8">
         <v>2370000</v>
       </c>
-      <c r="L8" s="8">
+      <c r="M8" s="8">
         <v>0</v>
       </c>
-      <c r="M8" s="7">
+      <c r="N8" s="7">
         <v>1</v>
       </c>
-      <c r="N8" s="8">
+      <c r="O8" s="8">
         <v>1</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="P8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="P8" s="12" t="s">
+      <c r="Q8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="R8" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="R8" s="12" t="s">
+      <c r="S8" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="S8" s="11" t="s">
+      <c r="T8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="T8" s="12" t="s">
+      <c r="U8" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B9" s="8">
         <v>4</v>
       </c>
@@ -3944,41 +3986,44 @@
       <c r="H9" s="7">
         <v>70</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="8">
+      <c r="L9" s="8">
         <v>2210000</v>
       </c>
-      <c r="L9" s="8">
+      <c r="M9" s="8">
         <v>0</v>
       </c>
-      <c r="M9" s="7">
+      <c r="N9" s="7">
         <v>1</v>
       </c>
-      <c r="N9" s="8">
+      <c r="O9" s="8">
         <v>1</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="P9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="P9" s="12" t="s">
+      <c r="Q9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Q9" s="11" t="s">
+      <c r="R9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="R9" s="12" t="s">
+      <c r="S9" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="S9" s="11" t="s">
+      <c r="T9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="T9" s="12" t="s">
+      <c r="U9" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B10" s="8">
         <v>5</v>
       </c>
@@ -4000,41 +4045,44 @@
       <c r="H10" s="7">
         <v>70</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K10" s="8">
+      <c r="L10" s="8">
         <v>2210000</v>
       </c>
-      <c r="L10" s="8">
+      <c r="M10" s="8">
         <v>0</v>
       </c>
-      <c r="M10" s="7">
+      <c r="N10" s="7">
         <v>0.6</v>
       </c>
-      <c r="N10" s="8">
+      <c r="O10" s="8">
         <v>0</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="P10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="P10" s="12" t="s">
+      <c r="Q10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="R10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="R10" s="12" t="s">
+      <c r="S10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="S10" s="11" t="s">
+      <c r="T10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="T10" s="12" t="s">
+      <c r="U10" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B11" s="8">
         <v>6</v>
       </c>
@@ -4056,41 +4104,44 @@
       <c r="H11" s="7">
         <v>70</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K11" s="8">
+      <c r="L11" s="8">
         <v>2210000</v>
       </c>
-      <c r="L11" s="8">
+      <c r="M11" s="8">
         <v>0</v>
       </c>
-      <c r="M11" s="7">
+      <c r="N11" s="7">
         <v>1</v>
       </c>
-      <c r="N11" s="8">
+      <c r="O11" s="8">
         <v>1</v>
       </c>
-      <c r="O11" s="11" t="s">
+      <c r="P11" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="P11" s="12" t="s">
+      <c r="Q11" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Q11" s="11" t="s">
+      <c r="R11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="R11" s="12" t="s">
+      <c r="S11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="S11" s="11" t="s">
+      <c r="T11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="T11" s="12" t="s">
+      <c r="U11" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B12" s="8">
         <v>7</v>
       </c>
@@ -4112,41 +4163,44 @@
       <c r="H12" s="7">
         <v>70</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" t="s">
+        <v>84</v>
+      </c>
+      <c r="K12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="8">
+      <c r="L12" s="8">
         <v>2050000</v>
       </c>
-      <c r="L12" s="8">
+      <c r="M12" s="8">
         <v>0</v>
       </c>
-      <c r="M12" s="7">
+      <c r="N12" s="7">
         <v>1</v>
       </c>
-      <c r="N12" s="8">
+      <c r="O12" s="8">
         <v>1</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="P12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="P12" s="12" t="s">
+      <c r="Q12" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Q12" s="11" t="s">
+      <c r="R12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="R12" s="12" t="s">
+      <c r="S12" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="S12" s="11" t="s">
+      <c r="T12" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="T12" s="12" t="s">
+      <c r="U12" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B13" s="8">
         <v>8</v>
       </c>
@@ -4166,43 +4220,46 @@
         <v>50</v>
       </c>
       <c r="H13" s="7">
-        <v>70</v>
-      </c>
-      <c r="J13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K13" s="8">
-        <v>1790000</v>
-      </c>
-      <c r="L13" s="10">
+      <c r="L13" s="8">
+        <v>1753000</v>
+      </c>
+      <c r="M13" s="10">
         <v>10</v>
       </c>
-      <c r="M13" s="7">
+      <c r="N13" s="7">
         <v>1</v>
       </c>
-      <c r="N13" s="8">
-        <v>1</v>
-      </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="8">
+        <v>2</v>
+      </c>
+      <c r="P13" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="P13" s="12" t="s">
+      <c r="Q13" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Q13" s="11" t="s">
+      <c r="R13" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="R13" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="S13" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="T13" s="12" t="s">
-        <v>25</v>
+      <c r="S13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="U13" s="12" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B14" s="8">
         <v>9</v>
       </c>
@@ -4219,46 +4276,49 @@
         <v>60</v>
       </c>
       <c r="G14" s="7">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H14" s="7">
         <v>70</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K14" s="8">
-        <v>1910000</v>
-      </c>
-      <c r="L14" s="10">
+      <c r="L14" s="8">
+        <v>1790000</v>
+      </c>
+      <c r="M14" s="10">
+        <v>10</v>
+      </c>
+      <c r="N14" s="7">
+        <v>1</v>
+      </c>
+      <c r="O14" s="8">
+        <v>1</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="R14" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="M14" s="7">
-        <v>1</v>
-      </c>
-      <c r="N14" s="8">
-        <v>1</v>
-      </c>
-      <c r="O14" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="P14" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q14" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="R14" s="12" t="s">
+      <c r="S14" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="S14" s="11" t="s">
+      <c r="T14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="T14" s="12" t="s">
+      <c r="U14" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B15" s="8">
         <v>10</v>
       </c>
@@ -4275,49 +4335,52 @@
         <v>60</v>
       </c>
       <c r="G15" s="7">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H15" s="7">
-        <v>50</v>
-      </c>
-      <c r="J15" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J15" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="8">
-        <v>1753000</v>
-      </c>
-      <c r="L15" s="10">
-        <v>10</v>
-      </c>
-      <c r="M15" s="7">
+      <c r="L15" s="8">
+        <v>1910000</v>
+      </c>
+      <c r="M15" s="10">
+        <v>20</v>
+      </c>
+      <c r="N15" s="7">
         <v>1</v>
       </c>
-      <c r="N15" s="8">
-        <v>2</v>
-      </c>
-      <c r="O15" s="11" t="s">
+      <c r="O15" s="8">
+        <v>1</v>
+      </c>
+      <c r="P15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="P15" s="12" t="s">
+      <c r="Q15" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Q15" s="11" t="s">
+      <c r="R15" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="R15" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="S15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="T15" s="12" t="s">
-        <v>22</v>
+      <c r="S15" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="T15" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="U15" s="12" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="P6:P15 R6:R15 T6:T15" numberStoredAsText="1"/>
+    <ignoredError sqref="Q15 S15 U15 U14 S14 Q14 Q6:Q12 S6:S12 U6:U12" numberStoredAsText="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
